--- a/02-formulas-functions/03-date-time-functions/2.3-date-time-functions.xlsx
+++ b/02-formulas-functions/03-date-time-functions/2.3-date-time-functions.xlsx
@@ -1258,7 +1258,7 @@
       </c>
       <c r="F5" s="19" t="inlineStr">
         <is>
-          <t>The whole part, 45,658, is the date serial number: January 1, 2025 is day 45,658 counting from January 1, 1900. The decimal part, 0.8812, is the time as a fraction of a 24-hour day: 21:09 is 1,269 minutes ÷ 1,440 minutes per day. You can also see the number by giving the cell the General format (Ctrl + Shift + ~, or Control + Shift + ~ on a Mac). Because dates and times are numbers, you can add, subtract, and compare them.</t>
+          <t>The whole part, 45,658, is the date serial number: January 1, 2025 is day 45,658 counting from January 1, 1900. The decimal part, 0.8812, is the time as a fraction of a 24-hour day: 21:09 is 1,269 minutes ÷ 1,440 minutes per day. You can also see the number by giving the cell the General format with Ctrl + Shift + ~ (Mac: Control + Shift + ~). Because dates and times are numbers, you can add, subtract, and compare them.</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>The patient in Stays row 15 (encounter ENC110973) was 64 at admission. On what date does the patient turn 65 and become age-eligible for Medicare? Use the DOB in that row.</t>
+          <t>The patient in Stays row 15 (encounter ENC110973) was 64 at admission. On what date does the patient turn 65, the usual age of Medicare eligibility? Use the DOB in that row.</t>
         </is>
       </c>
       <c r="C6" s="47" t="n">
@@ -1465,7 +1465,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="96" customHeight="1">
+    <row r="13" ht="111" customHeight="1">
       <c r="A13" s="18" t="inlineStr">
         <is>
           <t>9</t>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="F13" s="19" t="inlineStr">
         <is>
-          <t>An empty PaidDate counts as 0 in arithmetic, so a bare =G2-F2 returns minus the submit date's serial number for every unpaid claim (−45,666 for the first one), which wrecks the average. The IF returns empty text for those rows, and AVERAGE ignores text. =DAYS(G2,F2) gives the same number of days. Notice that DAYS takes the end date first.</t>
+          <t>An empty PaidDate counts as 0 in arithmetic, so a bare =G2-F2 returns minus the submit date's serial number for every unpaid claim (−45,666 for the first one), which wrecks the average. The IF returns empty text for those rows, and AVERAGE ignores text. =IF(G2="","",DAYS(G2,F2)) gives the same result. Notice that DAYS takes the end date first, and that it needs the same blank guard.</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B17" s="19" t="inlineStr">
         <is>
-          <t>The Shifts sheet's ClockIn and ClockOut columns hold clock times only, with no dates, and 69 shifts end after midnight. Fill the yellow PaidTime column with each shift's paid time: clock-out minus clock-in, corrected for shifts that cross midnight, minus a 30-minute unpaid meal break. Start in H2. The gray cell totals your column in [h]:mm format. What is the total paid time for the week?</t>
+          <t>The Shifts sheet's ClockIn and ClockOut columns hold clock times only, with no dates, and 69 shifts end after midnight. Fill the yellow PaidTime column with each shift's paid time: clock-out minus clock-in, corrected for shifts that cross midnight, minus a 30-minute unpaid meal break. Keep each result as a time value (don't multiply by 24). Start in H2. The gray cell totals your column in [h]:mm format. What is the total paid time for the week?</t>
         </is>
       </c>
       <c r="C17" s="55" t="n">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
-          <t>The patient in Stays row 15 (encounter ENC110973) was 64 at admission. On what date does the patient turn 65 and become age-eligible for Medicare? Use the DOB in that row.</t>
+          <t>The patient in Stays row 15 (encounter ENC110973) was 64 at admission. On what date does the patient turn 65, the usual age of Medicare eligibility? Use the DOB in that row.</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>The Shifts sheet's ClockIn and ClockOut columns hold clock times only, with no dates, and 69 shifts end after midnight. Fill the yellow PaidTime column with each shift's paid time: clock-out minus clock-in, corrected for shifts that cross midnight, minus a 30-minute unpaid meal break. Start in H2. The gray cell totals your column in [h]:mm format. What is the total paid time for the week?</t>
+          <t>The Shifts sheet's ClockIn and ClockOut columns hold clock times only, with no dates, and 69 shifts end after midnight. Fill the yellow PaidTime column with each shift's paid time: clock-out minus clock-in, corrected for shifts that cross midnight, minus a 30-minute unpaid meal break. Keep each result as a time value (don't multiply by 24). Start in H2. The gray cell totals your column in [h]:mm format. What is the total paid time for the week?</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -40749,7 +40749,7 @@
     <row r="2" ht="79" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>Ashby Falls' utilization review nurse is preparing for a Medicare audit. Under the CMS two-midnight benchmark, an inpatient admission is generally expected to span at least two midnights of hospital care. This bonus uses a simplified, educational version (not billing guidance): count the midnights between two date-times by comparing their dates, not the hours between them. The nurse also wants to know whether the day of the week a patient is admitted affects how long they stay. Fill the yellow Midnights, BenchMidnights, and AdmitDay columns on the Stays sheet as you go. B2 and B4 also use your LOSDays column from task 7.</t>
+          <t>Ashby Falls' utilization review nurse is preparing for a Medicare audit. Under the CMS two-midnight benchmark, an inpatient admission is generally expected to span at least two midnights of hospital care. This bonus uses a simplified, educational version (not billing guidance): count the midnights between two date-times by comparing their dates, not the hours between them. The nurse also wants to know whether the day of the week a patient is admitted affects how long they stay. Fill the yellow Midnights, BenchMidnights, and AdmitDay columns on the Stays sheet as you go. B2, B4, and B5 also use your LOSDays column from task 7.</t>
         </is>
       </c>
     </row>

--- a/02-formulas-functions/03-date-time-functions/2.3-date-time-functions.xlsx
+++ b/02-formulas-functions/03-date-time-functions/2.3-date-time-functions.xlsx
@@ -54,7 +54,7 @@
     <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="167" formatCode="mm/dd/yyyy hh:mm"/>
     <numFmt numFmtId="168" formatCode="hh:mm"/>
-    <numFmt numFmtId="169" formatCode="0.0000"/>
+    <numFmt numFmtId="169" formatCode="0.00000"/>
     <numFmt numFmtId="170" formatCode="0.0"/>
     <numFmt numFmtId="171" formatCode="[h]:mm"/>
   </numFmts>
@@ -217,7 +217,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -297,6 +297,7 @@
     <xf numFmtId="2" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="20" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
@@ -1147,7 +1148,7 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>All 369 inpatient stays admitted at Ashby Falls Community Hospital in 2025 (with each patient's date of birth and, for ED admissions, the ED arrival time) and the insurance claim for each stay; the hospital's 226 emergency department visits in Q4 2025; one pay week (December 14–20, 2025) of worked shifts on Medical-Surgical 4 West at Bluestone Memorial Hospital; and the business office's 2025–2026 holiday calendar.</t>
+          <t>All 369 inpatient stays admitted at Ashby Falls Community Hospital in 2025 (with each patient's date of birth and, for ED admissions, the ED arrival time), the insurance claim for each stay, and the hospital's 226 emergency department visits in Q4 2025. The workbook also has one pay week (December 14–20, 2025) of worked shifts on Medical-Surgical 4 West at Bluestone Memorial Hospital and the business office's 2025–2026 holiday calendar.</t>
         </is>
       </c>
     </row>
@@ -1188,46 +1189,46 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="41" t="inlineStr">
+      <c r="A1" s="42" t="inlineStr">
         <is>
           <t>🔑 Answer Key — Lesson 2.3</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="42" t="inlineStr">
+      <c r="A2" s="43" t="inlineStr">
         <is>
           <t>Spoiler alert — try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution; column E is that same formula, live, proving it works.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="43" t="inlineStr">
+      <c r="A4" s="44" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="43" t="inlineStr">
+      <c r="B4" s="44" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="C4" s="43" t="inlineStr">
+      <c r="C4" s="44" t="inlineStr">
         <is>
           <t>Answer</t>
         </is>
       </c>
-      <c r="D4" s="43" t="inlineStr">
+      <c r="D4" s="44" t="inlineStr">
         <is>
           <t>Sample solution</t>
         </is>
       </c>
-      <c r="E4" s="43" t="inlineStr">
+      <c r="E4" s="44" t="inlineStr">
         <is>
           <t>Live result</t>
         </is>
       </c>
-      <c r="F4" s="43" t="inlineStr">
+      <c r="F4" s="44" t="inlineStr">
         <is>
           <t>Explanation</t>
         </is>
@@ -1241,24 +1242,24 @@
       </c>
       <c r="B5" s="19" t="inlineStr">
         <is>
-          <t>Stays!G2 shows the first admission of 2025: 01/01/2025 21:09. What number does Excel actually store in that cell? Point a formula at the cell (the answer cell is already formatted to show 4 decimal places).</t>
-        </is>
-      </c>
-      <c r="C5" s="44" t="n">
+          <t>Stays!G2 shows the first admission of 2025: 01/01/2025 21:09. What number does Excel actually store in that cell? Enter a formula that refers to the cell. The answer cell is already formatted to show 5 decimal places, so you'll see the stored number instead of a date.</t>
+        </is>
+      </c>
+      <c r="C5" s="45" t="n">
         <v>45658.88125</v>
       </c>
-      <c r="D5" s="45" t="inlineStr">
+      <c r="D5" s="46" t="inlineStr">
         <is>
           <t>=Stays!G2</t>
         </is>
       </c>
-      <c r="E5" cm="1" s="46">
+      <c r="E5" cm="1" s="47">
         <f t="array" ref="E5">Stays!G2</f>
         <v/>
       </c>
       <c r="F5" s="19" t="inlineStr">
         <is>
-          <t>The whole part, 45,658, is the date serial number: January 1, 2025 is day 45,658 counting from January 1, 1900. The decimal part, 0.8812, is the time as a fraction of a 24-hour day: 21:09 is 1,269 minutes ÷ 1,440 minutes per day. You can also see the number by giving the cell the General format with Ctrl + Shift + ~ (Mac: Control + Shift + ~). Because dates and times are numbers, you can add, subtract, and compare them.</t>
+          <t>The whole part, 45,658, is the date serial number: January 1, 2025 is day 45,658 counting from January 1, 1900. The decimal part, 0.88125, is the time as a fraction of a 24-hour day: 21:09 is 1,269 minutes ÷ 1,440 minutes per day. You can also see the number by giving the cell the General format with Ctrl + Shift + ~ (Mac: Control + Shift + ~). Because dates and times are numbers, you can add, subtract, and compare them.</t>
         </is>
       </c>
     </row>
@@ -1273,15 +1274,15 @@
           <t>The patient in Stays row 15 (encounter ENC110973) was 64 at admission. On what date does the patient turn 65, the usual age of Medicare eligibility? Use the DOB in that row.</t>
         </is>
       </c>
-      <c r="C6" s="47" t="n">
+      <c r="C6" s="48" t="n">
         <v>45735</v>
       </c>
-      <c r="D6" s="45" t="inlineStr">
+      <c r="D6" s="46" t="inlineStr">
         <is>
           <t>=EDATE(Stays!E15,65*12)</t>
         </is>
       </c>
-      <c r="E6" cm="1" s="48">
+      <c r="E6" cm="1" s="49">
         <f t="array" ref="E6">EDATE(Stays!E15,65*12)</f>
         <v/>
       </c>
@@ -1302,15 +1303,15 @@
           <t>Fill the yellow AgeAtAdmit column on the Stays sheet with each patient's age in completed years on the admit date. Start in I2. The gray cell averages your column. What was the average age at admission?</t>
         </is>
       </c>
-      <c r="C7" s="49" t="n">
+      <c r="C7" s="50" t="n">
         <v>58.12466124661247</v>
       </c>
-      <c r="D7" s="45" t="inlineStr">
+      <c r="D7" s="46" t="inlineStr">
         <is>
           <t>=DATEDIF(E2,G2,"Y")</t>
         </is>
       </c>
-      <c r="E7" cm="1" s="50">
+      <c r="E7" cm="1" s="51">
         <f t="array" ref="E7">SUMPRODUCT(YEAR(Stays!G2:G370)-YEAR(Stays!E2:E370)-((MONTH(Stays!G2:G370)*100+DAY(Stays!G2:G370))&lt;(MONTH(Stays!E2:E370)*100+DAY(Stays!E2:E370))))/COUNT(Stays!E2:E370)</f>
         <v/>
       </c>
@@ -1331,15 +1332,15 @@
           <t>The youngest patient (Stays row 42, encounter ENC112029) was an infant. Calculate the exact age in years at admission with YEARFRAC, using basis 1 (actual/actual). Round to 2 decimal places.</t>
         </is>
       </c>
-      <c r="C8" s="49" t="n">
+      <c r="C8" s="50" t="n">
         <v>0.7</v>
       </c>
-      <c r="D8" s="45" t="inlineStr">
+      <c r="D8" s="46" t="inlineStr">
         <is>
           <t>=ROUND(YEARFRAC(Stays!E42,Stays!G42,1),2)</t>
         </is>
       </c>
-      <c r="E8" cm="1" s="50">
+      <c r="E8" cm="1" s="51">
         <f t="array" ref="E8">ROUND(YEARFRAC(Stays!E42,Stays!G42,1),2)</f>
         <v/>
       </c>
@@ -1360,15 +1361,15 @@
           <t>How many stays were admitted on a weekend (Saturday or Sunday)? Use the AdmitDateTime column.</t>
         </is>
       </c>
-      <c r="C9" s="51" t="n">
+      <c r="C9" s="52" t="n">
         <v>95</v>
       </c>
-      <c r="D9" s="45" t="inlineStr">
+      <c r="D9" s="46" t="inlineStr">
         <is>
           <t>=SUMPRODUCT(--(WEEKDAY(Stays!G2:G370,2)&gt;5))</t>
         </is>
       </c>
-      <c r="E9" cm="1" s="52">
+      <c r="E9" cm="1" s="53">
         <f t="array" ref="E9">SUMPRODUCT(--(WEEKDAY(Stays!G2:G370,2)&gt;5))</f>
         <v/>
       </c>
@@ -1389,15 +1390,15 @@
           <t>How many stays were admitted in April 2025? Compare AdmitDateTime with dates you build with DATE.</t>
         </is>
       </c>
-      <c r="C10" s="51" t="n">
+      <c r="C10" s="52" t="n">
         <v>27</v>
       </c>
-      <c r="D10" s="45" t="inlineStr">
+      <c r="D10" s="46" t="inlineStr">
         <is>
           <t>=SUMPRODUCT((Stays!G2:G370&gt;=DATE(2025,4,1))*(Stays!G2:G370&lt;DATE(2025,5,1)))</t>
         </is>
       </c>
-      <c r="E10" cm="1" s="52">
+      <c r="E10" cm="1" s="53">
         <f t="array" ref="E10">SUMPRODUCT((Stays!G2:G370&gt;=DATE(2025,4,1))*(Stays!G2:G370&lt;DATE(2025,5,1)))</f>
         <v/>
       </c>
@@ -1418,21 +1419,21 @@
           <t>Fill the yellow LOSDays column with each stay's length of stay in days, including the fraction of a day (DischargeDateTime minus AdmitDateTime). Start in J2. The gray cell averages your column. What was the average length of stay?</t>
         </is>
       </c>
-      <c r="C11" s="49" t="n">
+      <c r="C11" s="50" t="n">
         <v>4.544229900632341</v>
       </c>
-      <c r="D11" s="45" t="inlineStr">
+      <c r="D11" s="46" t="inlineStr">
         <is>
           <t>=H2-G2</t>
         </is>
       </c>
-      <c r="E11" cm="1" s="50">
+      <c r="E11" cm="1" s="51">
         <f t="array" ref="E11">(SUM(Stays!H2:H370)-SUM(Stays!G2:G370))/COUNT(Stays!G2:G370)</f>
         <v/>
       </c>
       <c r="F11" s="19" t="inlineStr">
         <is>
-          <t>Subtracting two date-times gives the elapsed days, with the hours as a decimal: 2.50 is two and a half days. In a cell with the General format, Excel may copy the date format from the cells you referenced and show 4.5 days as 01/04/1900 12:00. Change the format to Number when that happens. Multiply by 24 to get hours. The live formula in the key uses a shortcut: the sum of the differences equals the difference of the sums.</t>
+          <t>Subtracting two date-times gives the elapsed days, with the hours as a decimal: 2.50 is two and a half days. The LOSDays column is already formatted as a number. In a General cell, Excel may copy the date format from the cells you referenced and show 4.5 days as 01/04/1900 12:00, so change the format to Number when that happens. Multiply by 24 to get hours. The live formula in the key uses a shortcut: the sum of the differences equals the difference of the sums.</t>
         </is>
       </c>
     </row>
@@ -1447,15 +1448,15 @@
           <t>Ashby Falls' billing standard says a claim must be submitted by the last day of the month after the month of service. What is the deadline for claim CLM511227 (Claims row 29, ServiceDate 01/30/2025)?</t>
         </is>
       </c>
-      <c r="C12" s="47" t="n">
+      <c r="C12" s="48" t="n">
         <v>45716</v>
       </c>
-      <c r="D12" s="45" t="inlineStr">
+      <c r="D12" s="46" t="inlineStr">
         <is>
           <t>=EOMONTH(Claims!E29,1)</t>
         </is>
       </c>
-      <c r="E12" cm="1" s="48">
+      <c r="E12" cm="1" s="49">
         <f t="array" ref="E12">EOMONTH(Claims!E29,1)</f>
         <v/>
       </c>
@@ -1476,15 +1477,15 @@
           <t>Fill the yellow DaysToPay column on the Claims sheet with the calendar days from SubmitDate to PaidDate. 94 claims have no PaidDate yet, so make those rows return "" (empty text). Start in H2. The gray cell averages your column. What is the average days to pay?</t>
         </is>
       </c>
-      <c r="C13" s="53" t="n">
+      <c r="C13" s="54" t="n">
         <v>27.62181818181818</v>
       </c>
-      <c r="D13" s="45" t="inlineStr">
+      <c r="D13" s="46" t="inlineStr">
         <is>
           <t>=IF(G2="","",G2-F2)</t>
         </is>
       </c>
-      <c r="E13" cm="1" s="54">
+      <c r="E13" cm="1" s="55">
         <f t="array" ref="E13">SUMPRODUCT((Claims!G2:G370&lt;&gt;"")*(Claims!G2:G370-Claims!F2:F370))/COUNT(Claims!G2:G370)</f>
         <v/>
       </c>
@@ -1505,15 +1506,15 @@
           <t>Claim CLM520056 (Claims row 307) is still Pending. As of the report date in Settings!B2, how many business days has it been waiting? Count from its SubmitDate through the report date, both days included, skipping weekends and the dates on the Holidays sheet.</t>
         </is>
       </c>
-      <c r="C14" s="51" t="n">
+      <c r="C14" s="52" t="n">
         <v>28</v>
       </c>
-      <c r="D14" s="45" t="inlineStr">
+      <c r="D14" s="46" t="inlineStr">
         <is>
           <t>=NETWORKDAYS(Claims!F307,Settings!$B$2,Holidays!$A$2:$A$19)</t>
         </is>
       </c>
-      <c r="E14" cm="1" s="52">
+      <c r="E14" cm="1" s="53">
         <f t="array" ref="E14">NETWORKDAYS(Claims!F307,Settings!$B$2,Holidays!$A$2:$A$19)</f>
         <v/>
       </c>
@@ -1534,15 +1535,15 @@
           <t>Claim CLM517132 (Claims row 207) was only partially paid by Evergreen Mutual Insurance, and the payment posted on its PaidDate. Bluestone Health's policy gives the appeals team 10 business days to send an underpayment appeal, so the deadline is the 10th business day after the PaidDate (the PaidDate itself doesn't count). Weekends and the dates on the Holidays sheet aren't business days. What is the deadline?</t>
         </is>
       </c>
-      <c r="C15" s="47" t="n">
+      <c r="C15" s="48" t="n">
         <v>45994</v>
       </c>
-      <c r="D15" s="45" t="inlineStr">
+      <c r="D15" s="46" t="inlineStr">
         <is>
           <t>=WORKDAY(Claims!G207,10,Holidays!$A$2:$A$19)</t>
         </is>
       </c>
-      <c r="E15" cm="1" s="48">
+      <c r="E15" cm="1" s="49">
         <f t="array" ref="E15">WORKDAY(Claims!G207,10,Holidays!$A$2:$A$19)</f>
         <v/>
       </c>
@@ -1563,15 +1564,15 @@
           <t>Fill the yellow DoorToProviderMin column on the ED sheet with the minutes from ArrivalDateTime to ProviderSeenDateTime. 9 patients left without being seen and have no ProviderSeenDateTime, so make those rows return "". Start in H2. The gray cell averages your column. What is the average door-to-provider time in minutes?</t>
         </is>
       </c>
-      <c r="C16" s="53" t="n">
+      <c r="C16" s="54" t="n">
         <v>49.14746543778802</v>
       </c>
-      <c r="D16" s="45" t="inlineStr">
+      <c r="D16" s="46" t="inlineStr">
         <is>
           <t>=IF(E2="","",(E2-C2)*1440)</t>
         </is>
       </c>
-      <c r="E16" cm="1" s="54">
+      <c r="E16" cm="1" s="55">
         <f t="array" ref="E16">SUMPRODUCT((ED!E2:E227&lt;&gt;"")*(ED!E2:E227-ED!C2:C227))*1440/COUNT(ED!E2:E227)</f>
         <v/>
       </c>
@@ -1581,7 +1582,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="156" customHeight="1">
+    <row r="17" ht="171" customHeight="1">
       <c r="A17" s="18" t="inlineStr">
         <is>
           <t>13</t>
@@ -1592,21 +1593,21 @@
           <t>The Shifts sheet's ClockIn and ClockOut columns hold clock times only, with no dates, and 69 shifts end after midnight. Fill the yellow PaidTime column with each shift's paid time: clock-out minus clock-in, corrected for shifts that cross midnight, minus a 30-minute unpaid meal break. Keep each result as a time value (don't multiply by 24). Start in H2. The gray cell totals your column in [h]:mm format. What is the total paid time for the week?</t>
         </is>
       </c>
-      <c r="C17" s="55" t="n">
+      <c r="C17" s="56" t="n">
         <v>92.24166666666666</v>
       </c>
-      <c r="D17" s="45" t="inlineStr">
+      <c r="D17" s="46" t="inlineStr">
         <is>
           <t>=MOD(G2-F2,1)-TIME(0,30,0)</t>
         </is>
       </c>
-      <c r="E17" cm="1" s="56">
+      <c r="E17" cm="1" s="57">
         <f t="array" ref="E17">SUMPRODUCT(MOD(Shifts!G2:G186-Shifts!F2:F186,1))-COUNT(Shifts!F2:F186)*TIME(0,30,0)</f>
         <v/>
       </c>
       <c r="F17" s="19" t="inlineStr">
         <is>
-          <t>Shift SH915484 clocked in at 18:48 and out at 08:20. 08:20 − 18:48 is negative (−0.4361 of a day). MOD(…, 1) adds one whole day to a negative result and leaves positive results alone, so the shift becomes 13:32. Subtract the meal break as a time, TIME(0,30,0) or "0:30" or 30/1440. Subtracting 0.5 would remove half a *day*. The total is 2,213.8 hours, so it needs [h]:mm. Plain h:mm would wrap past every 24 hours and show only the leftover hours. Without MOD the week totals 557.8 hours, because every overnight shift comes out negative. Format your column as [h]:mm (or h:mm) to read each shift.</t>
+          <t>Shift SH915484 clocked in at 18:48 and out at 08:20. 08:20 − 18:48 is negative (−0.4361 of a day). MOD(…, 1) adds one whole day to a negative result and leaves positive results alone, so the shift becomes 13:32. Subtract the meal break as a time, TIME(0,30,0) or "0:30" or 30/1440. Subtracting 0.5 would remove half a *day*. The total is 2,213.8 hours, so it needs [h]:mm. Plain h:mm would wrap past every 24 hours and show only the leftover hours. Without MOD the week totals 557.8 hours, because every overnight shift comes out negative. The PaidTime column is formatted h:mm, so a shift that comes out negative shows ######## instead of a time.</t>
         </is>
       </c>
     </row>
@@ -1638,46 +1639,46 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="41" t="inlineStr">
+      <c r="A1" s="42" t="inlineStr">
         <is>
           <t>🔑 Bonus Key — Lesson 2.3</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="42" t="inlineStr">
+      <c r="A2" s="43" t="inlineStr">
         <is>
           <t>Spoiler alert — try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution; column E is that same formula, live, proving it works.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="43" t="inlineStr">
+      <c r="A4" s="44" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="43" t="inlineStr">
+      <c r="B4" s="44" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="C4" s="43" t="inlineStr">
+      <c r="C4" s="44" t="inlineStr">
         <is>
           <t>Answer</t>
         </is>
       </c>
-      <c r="D4" s="43" t="inlineStr">
+      <c r="D4" s="44" t="inlineStr">
         <is>
           <t>Sample solution</t>
         </is>
       </c>
-      <c r="E4" s="43" t="inlineStr">
+      <c r="E4" s="44" t="inlineStr">
         <is>
           <t>Live result</t>
         </is>
       </c>
-      <c r="F4" s="43" t="inlineStr">
+      <c r="F4" s="44" t="inlineStr">
         <is>
           <t>Explanation</t>
         </is>
@@ -1694,15 +1695,15 @@
           <t>Fill the Midnights column with the number of midnights each stay crossed between AdmitDateTime and DischargeDateTime. Start in K2. The gray cell counts your rows with 2 or more. How many stays crossed at least two midnights?</t>
         </is>
       </c>
-      <c r="C5" s="51" t="n">
+      <c r="C5" s="52" t="n">
         <v>356</v>
       </c>
-      <c r="D5" s="45" t="inlineStr">
+      <c r="D5" s="46" t="inlineStr">
         <is>
           <t>=INT(H2)-INT(G2)</t>
         </is>
       </c>
-      <c r="E5" cm="1" s="52">
+      <c r="E5" cm="1" s="53">
         <f t="array" ref="E5">SUMPRODUCT(--((INT(Stays!H2:H370)-INT(Stays!G2:G370))&gt;=2))</f>
         <v/>
       </c>
@@ -1723,15 +1724,15 @@
           <t>How many stays crossed two or more midnights even though they lasted LESS than 48 hours?</t>
         </is>
       </c>
-      <c r="C6" s="51" t="n">
+      <c r="C6" s="52" t="n">
         <v>28</v>
       </c>
-      <c r="D6" s="45" t="inlineStr">
+      <c r="D6" s="46" t="inlineStr">
         <is>
           <t>=SUMPRODUCT((Stays!K2:K370&gt;=2)*(Stays!J2:J370&lt;2))</t>
         </is>
       </c>
-      <c r="E6" cm="1" s="52">
+      <c r="E6" cm="1" s="53">
         <f t="array" ref="E6">SUMPRODUCT(((INT(Stays!H2:H370)-INT(Stays!G2:G370))&gt;=2)*((Stays!H2:H370-Stays!G2:G370)&lt;2))</f>
         <v/>
       </c>
@@ -1752,15 +1753,15 @@
           <t>CMS starts the benchmark clock when hospital care begins, which for ED admissions is the ED arrival, not the inpatient admit order. Fill the BenchMidnights column: midnights from EDArrivalDateTime to DischargeDateTime, or from AdmitDateTime when EDArrivalDateTime is blank. Start in L2. The gray cell counts your rows with 2 or more. How many stays meet the benchmark when ED time counts?</t>
         </is>
       </c>
-      <c r="C7" s="51" t="n">
+      <c r="C7" s="52" t="n">
         <v>357</v>
       </c>
-      <c r="D7" s="45" t="inlineStr">
+      <c r="D7" s="46" t="inlineStr">
         <is>
           <t>=INT(H2)-INT(IF(F2="",G2,F2))</t>
         </is>
       </c>
-      <c r="E7" cm="1" s="52">
+      <c r="E7" cm="1" s="53">
         <f t="array" ref="E7">SUMPRODUCT(--((INT(Stays!H2:H370)-(INT(Stays!G2:G370)*(Stays!F2:F370="")+INT(Stays!F2:F370)*(Stays!F2:F370&lt;&gt;"")))&gt;=2))</f>
         <v/>
       </c>
@@ -1770,7 +1771,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="111" customHeight="1">
+    <row r="8" ht="141" customHeight="1">
       <c r="A8" s="18" t="inlineStr">
         <is>
           <t>B4</t>
@@ -1778,28 +1779,28 @@
       </c>
       <c r="B8" s="19" t="inlineStr">
         <is>
-          <t>Fill the AdmitDay column with the weekday name of each AdmitDateTime (Monday, Tuesday, …). What was the average length of stay, in HOURS, for patients admitted on a Friday? Round to 1 decimal place.</t>
-        </is>
-      </c>
-      <c r="C8" s="53" t="n">
+          <t>Fill the AdmitDay column with the weekday name of each AdmitDateTime (Monday, Tuesday, …). Start in M2. What was the average length of stay, in HOURS, for patients admitted on a Friday? Use your LOSDays column and round to 1 decimal place.</t>
+        </is>
+      </c>
+      <c r="C8" s="54" t="n">
         <v>108.3</v>
       </c>
-      <c r="D8" s="45" t="inlineStr">
+      <c r="D8" s="46" t="inlineStr">
         <is>
           <t>=ROUND(AVERAGEIF(Stays!M2:M370,"Friday",Stays!J2:J370)*24,1)</t>
         </is>
       </c>
-      <c r="E8" cm="1" s="54">
+      <c r="E8" cm="1" s="55">
         <f t="array" ref="E8">ROUND(SUMPRODUCT((WEEKDAY(Stays!G2:G370,2)=5)*(Stays!H2:H370-Stays!G2:G370))*24/SUMPRODUCT(--(WEEKDAY(Stays!G2:G370,2)=5)),1)</f>
         <v/>
       </c>
       <c r="F8" s="19" t="inlineStr">
         <is>
-          <t>Fill AdmitDay with =TEXT(G2,"dddd"), which returns full weekday names. AVERAGEIF averages the LOSDays values on rows where AdmitDay is "Friday", and × 24 converts days to hours. In Microsoft 365 and Excel 2021, =ROUND(AVERAGE(IF(Stays!M2:M370="Friday",Stays!J2:J370))*24,1) also works, as you saw in Lesson 2.1. TEXT returns weekday names in your Office language, so a German Excel shows "Freitag".</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="141" customHeight="1">
+          <t>Fill AdmitDay with =TEXT(G2,"dddd"), which returns full weekday names. AVERAGEIF averages the LOSDays values on rows where AdmitDay is "Friday", and × 24 converts days to hours. The array formula from Lesson 2.1, =ROUND(AVERAGE(IF(Stays!M2:M370="Friday",Stays!J2:J370))*24,1), also works. Microsoft 365 and Excel 2021 calculate it automatically, and Excel 2019 and earlier need Ctrl + Shift + Enter (Mac: ⌘ + Shift + Return). TEXT returns weekday names in your Office language, so a German Excel shows "Freitag".</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="156" customHeight="1">
       <c r="A9" s="18" t="inlineStr">
         <is>
           <t>B5</t>
@@ -1810,14 +1811,14 @@
           <t>Which weekday of admission has the LONGEST average length of stay? Type the weekday name.</t>
         </is>
       </c>
-      <c r="C9" s="51" t="inlineStr">
+      <c r="C9" s="52" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D9" s="45" t="inlineStr">
-        <is>
-          <t>1. On the Bonus sheet, type the seven weekday names, Monday to Sunday, in G2:G8.
+      <c r="D9" s="46" t="inlineStr">
+        <is>
+          <t>1. On the Bonus sheet, type Monday in G2 and drag the fill handle down to G8. AutoFill (Lesson 1.2) completes the week through Sunday.
 2. In H2, enter `=AVERAGEIF(Stays!$M$2:$M$370,G2,Stays!$J$2:$J$370)*24` and fill it down to H8.
 3. Find the largest average by eye, or let Excel find it: `=INDEX(G2:G8,MATCH(MAX(H2:H8),H2:H8,0))` (INDEX and MATCH are covered in Lesson 2.6).</t>
         </is>
@@ -1866,10 +1867,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="49" customHeight="1">
+    <row r="2" ht="79" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>Tasks 1–7 use the Stays sheet, 8–11 the Claims sheet, 12 the ED sheet, and 13 the Shifts sheet. Settings!B2 holds the report date (12/31/2025) and the Holidays sheet lists the business office's holidays. Several tasks ask you to fill a yellow column on a data sheet: type the formula in the first data row and the Table fills the rest (if it doesn't, double-click the fill handle). The gray cell on this sheet then summarizes your column.</t>
+          <t>Tasks 1–7 use the Stays sheet, 8–11 the Claims sheet, 12 the ED sheet, and 13 the Shifts sheet. Settings!B2 holds the report date (12/31/2025) and the Holidays sheet lists the business office's holidays. When a formula on this sheet points at a data sheet, include the sheet name, as in Stays!G2:G370, or click the cells on that sheet and Excel adds the name for you. (Selecting a whole Table column may write tblStays[AdmitDateTime] instead, which works the same.) Several tasks ask you to fill a yellow column on a data sheet: type the formula in the first data row and the Table fills the rest (if it doesn't, double-click the fill handle). The gray cell on this sheet then summarizes your column.</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1914,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="51" customHeight="1">
+    <row r="6" ht="66" customHeight="1">
       <c r="A6" s="18" t="inlineStr">
         <is>
           <t>1</t>
@@ -1921,7 +1922,7 @@
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>Stays!G2 shows the first admission of 2025: 01/01/2025 21:09. What number does Excel actually store in that cell? Point a formula at the cell (the answer cell is already formatted to show 4 decimal places).</t>
+          <t>Stays!G2 shows the first admission of 2025: 01/01/2025 21:09. What number does Excel actually store in that cell? Enter a formula that refers to the cell. The answer cell is already formatted to show 5 decimal places, so you'll see the stored number instead of a date.</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -34464,7 +34465,7 @@
       <c r="G2" s="36" t="n">
         <v>0.8145833333333333</v>
       </c>
-      <c r="H2" s="35" t="n"/>
+      <c r="H2" s="37" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -34496,7 +34497,7 @@
       <c r="G3" s="36" t="n">
         <v>0.8194444444444444</v>
       </c>
-      <c r="H3" s="35" t="n"/>
+      <c r="H3" s="37" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -34528,7 +34529,7 @@
       <c r="G4" s="36" t="n">
         <v>0.8138888888888889</v>
       </c>
-      <c r="H4" s="35" t="n"/>
+      <c r="H4" s="37" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -34560,7 +34561,7 @@
       <c r="G5" s="36" t="n">
         <v>0.8194444444444444</v>
       </c>
-      <c r="H5" s="35" t="n"/>
+      <c r="H5" s="37" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -34592,7 +34593,7 @@
       <c r="G6" s="36" t="n">
         <v>0.8180555555555555</v>
       </c>
-      <c r="H6" s="35" t="n"/>
+      <c r="H6" s="37" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -34624,7 +34625,7 @@
       <c r="G7" s="36" t="n">
         <v>0.8138888888888889</v>
       </c>
-      <c r="H7" s="35" t="n"/>
+      <c r="H7" s="37" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -34656,7 +34657,7 @@
       <c r="G8" s="36" t="n">
         <v>0.8159722222222222</v>
       </c>
-      <c r="H8" s="35" t="n"/>
+      <c r="H8" s="37" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -34688,7 +34689,7 @@
       <c r="G9" s="36" t="n">
         <v>0.8097222222222222</v>
       </c>
-      <c r="H9" s="35" t="n"/>
+      <c r="H9" s="37" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -34720,7 +34721,7 @@
       <c r="G10" s="36" t="n">
         <v>0.8173611111111111</v>
       </c>
-      <c r="H10" s="35" t="n"/>
+      <c r="H10" s="37" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -34752,7 +34753,7 @@
       <c r="G11" s="36" t="n">
         <v>0.8208333333333333</v>
       </c>
-      <c r="H11" s="35" t="n"/>
+      <c r="H11" s="37" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -34784,7 +34785,7 @@
       <c r="G12" s="36" t="n">
         <v>0.88125</v>
       </c>
-      <c r="H12" s="35" t="n"/>
+      <c r="H12" s="37" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -34816,7 +34817,7 @@
       <c r="G13" s="36" t="n">
         <v>0.8138888888888889</v>
       </c>
-      <c r="H13" s="35" t="n"/>
+      <c r="H13" s="37" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -34848,7 +34849,7 @@
       <c r="G14" s="36" t="n">
         <v>0.8159722222222222</v>
       </c>
-      <c r="H14" s="35" t="n"/>
+      <c r="H14" s="37" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -34880,7 +34881,7 @@
       <c r="G15" s="36" t="n">
         <v>0.8215277777777777</v>
       </c>
-      <c r="H15" s="35" t="n"/>
+      <c r="H15" s="37" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -34912,7 +34913,7 @@
       <c r="G16" s="36" t="n">
         <v>0.8458333333333333</v>
       </c>
-      <c r="H16" s="35" t="n"/>
+      <c r="H16" s="37" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -34944,7 +34945,7 @@
       <c r="G17" s="36" t="n">
         <v>0.6506944444444445</v>
       </c>
-      <c r="H17" s="35" t="n"/>
+      <c r="H17" s="37" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -34976,7 +34977,7 @@
       <c r="G18" s="36" t="n">
         <v>0.6486111111111111</v>
       </c>
-      <c r="H18" s="35" t="n"/>
+      <c r="H18" s="37" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -35008,7 +35009,7 @@
       <c r="G19" s="36" t="n">
         <v>0.8201388888888889</v>
       </c>
-      <c r="H19" s="35" t="n"/>
+      <c r="H19" s="37" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -35040,7 +35041,7 @@
       <c r="G20" s="36" t="n">
         <v>0.3472222222222222</v>
       </c>
-      <c r="H20" s="35" t="n"/>
+      <c r="H20" s="37" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -35072,7 +35073,7 @@
       <c r="G21" s="36" t="n">
         <v>0.31875</v>
       </c>
-      <c r="H21" s="35" t="n"/>
+      <c r="H21" s="37" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -35104,7 +35105,7 @@
       <c r="G22" s="36" t="n">
         <v>0.3208333333333334</v>
       </c>
-      <c r="H22" s="35" t="n"/>
+      <c r="H22" s="37" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -35136,7 +35137,7 @@
       <c r="G23" s="36" t="n">
         <v>0.3159722222222222</v>
       </c>
-      <c r="H23" s="35" t="n"/>
+      <c r="H23" s="37" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -35168,7 +35169,7 @@
       <c r="G24" s="36" t="n">
         <v>0.3215277777777778</v>
       </c>
-      <c r="H24" s="35" t="n"/>
+      <c r="H24" s="37" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -35200,7 +35201,7 @@
       <c r="G25" s="36" t="n">
         <v>0.3368055555555556</v>
       </c>
-      <c r="H25" s="35" t="n"/>
+      <c r="H25" s="37" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -35232,7 +35233,7 @@
       <c r="G26" s="36" t="n">
         <v>0.3166666666666667</v>
       </c>
-      <c r="H26" s="35" t="n"/>
+      <c r="H26" s="37" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -35264,7 +35265,7 @@
       <c r="G27" s="36" t="n">
         <v>0.3506944444444444</v>
       </c>
-      <c r="H27" s="35" t="n"/>
+      <c r="H27" s="37" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -35296,7 +35297,7 @@
       <c r="G28" s="36" t="n">
         <v>0.3229166666666667</v>
       </c>
-      <c r="H28" s="35" t="n"/>
+      <c r="H28" s="37" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -35328,7 +35329,7 @@
       <c r="G29" s="36" t="n">
         <v>0.3173611111111111</v>
       </c>
-      <c r="H29" s="35" t="n"/>
+      <c r="H29" s="37" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -35360,7 +35361,7 @@
       <c r="G30" s="36" t="n">
         <v>0.3208333333333334</v>
       </c>
-      <c r="H30" s="35" t="n"/>
+      <c r="H30" s="37" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -35392,7 +35393,7 @@
       <c r="G31" s="36" t="n">
         <v>0.3194444444444444</v>
       </c>
-      <c r="H31" s="35" t="n"/>
+      <c r="H31" s="37" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -35424,7 +35425,7 @@
       <c r="G32" s="36" t="n">
         <v>0.3506944444444444</v>
       </c>
-      <c r="H32" s="35" t="n"/>
+      <c r="H32" s="37" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -35456,7 +35457,7 @@
       <c r="G33" s="36" t="n">
         <v>0.8243055555555555</v>
       </c>
-      <c r="H33" s="35" t="n"/>
+      <c r="H33" s="37" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -35488,7 +35489,7 @@
       <c r="G34" s="36" t="n">
         <v>0.8131944444444444</v>
       </c>
-      <c r="H34" s="35" t="n"/>
+      <c r="H34" s="37" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -35520,7 +35521,7 @@
       <c r="G35" s="36" t="n">
         <v>0.8201388888888889</v>
       </c>
-      <c r="H35" s="35" t="n"/>
+      <c r="H35" s="37" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -35552,7 +35553,7 @@
       <c r="G36" s="36" t="n">
         <v>0.8111111111111111</v>
       </c>
-      <c r="H36" s="35" t="n"/>
+      <c r="H36" s="37" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -35584,7 +35585,7 @@
       <c r="G37" s="36" t="n">
         <v>0.8402777777777778</v>
       </c>
-      <c r="H37" s="35" t="n"/>
+      <c r="H37" s="37" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -35616,7 +35617,7 @@
       <c r="G38" s="36" t="n">
         <v>0.8138888888888889</v>
       </c>
-      <c r="H38" s="35" t="n"/>
+      <c r="H38" s="37" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -35648,7 +35649,7 @@
       <c r="G39" s="36" t="n">
         <v>0.8222222222222222</v>
       </c>
-      <c r="H39" s="35" t="n"/>
+      <c r="H39" s="37" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -35680,7 +35681,7 @@
       <c r="G40" s="36" t="n">
         <v>0.8152777777777778</v>
       </c>
-      <c r="H40" s="35" t="n"/>
+      <c r="H40" s="37" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -35712,7 +35713,7 @@
       <c r="G41" s="36" t="n">
         <v>0.8125</v>
       </c>
-      <c r="H41" s="35" t="n"/>
+      <c r="H41" s="37" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -35744,7 +35745,7 @@
       <c r="G42" s="36" t="n">
         <v>0.9756944444444444</v>
       </c>
-      <c r="H42" s="35" t="n"/>
+      <c r="H42" s="37" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -35776,7 +35777,7 @@
       <c r="G43" s="36" t="n">
         <v>0.8159722222222222</v>
       </c>
-      <c r="H43" s="35" t="n"/>
+      <c r="H43" s="37" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -35808,7 +35809,7 @@
       <c r="G44" s="36" t="n">
         <v>0.8361111111111111</v>
       </c>
-      <c r="H44" s="35" t="n"/>
+      <c r="H44" s="37" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -35840,7 +35841,7 @@
       <c r="G45" s="36" t="n">
         <v>0.6465277777777778</v>
       </c>
-      <c r="H45" s="35" t="n"/>
+      <c r="H45" s="37" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -35872,7 +35873,7 @@
       <c r="G46" s="36" t="n">
         <v>0.6451388888888889</v>
       </c>
-      <c r="H46" s="35" t="n"/>
+      <c r="H46" s="37" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -35904,7 +35905,7 @@
       <c r="G47" s="36" t="n">
         <v>0.8097222222222222</v>
       </c>
-      <c r="H47" s="35" t="n"/>
+      <c r="H47" s="37" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -35936,7 +35937,7 @@
       <c r="G48" s="36" t="n">
         <v>0.9881944444444445</v>
       </c>
-      <c r="H48" s="35" t="n"/>
+      <c r="H48" s="37" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -35968,7 +35969,7 @@
       <c r="G49" s="36" t="n">
         <v>0.3194444444444444</v>
       </c>
-      <c r="H49" s="35" t="n"/>
+      <c r="H49" s="37" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -36000,7 +36001,7 @@
       <c r="G50" s="36" t="n">
         <v>0.3097222222222222</v>
       </c>
-      <c r="H50" s="35" t="n"/>
+      <c r="H50" s="37" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -36032,7 +36033,7 @@
       <c r="G51" s="36" t="n">
         <v>0.3354166666666666</v>
       </c>
-      <c r="H51" s="35" t="n"/>
+      <c r="H51" s="37" t="n"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -36064,7 +36065,7 @@
       <c r="G52" s="36" t="n">
         <v>0.3152777777777778</v>
       </c>
-      <c r="H52" s="35" t="n"/>
+      <c r="H52" s="37" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -36096,7 +36097,7 @@
       <c r="G53" s="36" t="n">
         <v>0.3152777777777778</v>
       </c>
-      <c r="H53" s="35" t="n"/>
+      <c r="H53" s="37" t="n"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -36128,7 +36129,7 @@
       <c r="G54" s="36" t="n">
         <v>0.3138888888888889</v>
       </c>
-      <c r="H54" s="35" t="n"/>
+      <c r="H54" s="37" t="n"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -36160,7 +36161,7 @@
       <c r="G55" s="36" t="n">
         <v>0.3118055555555556</v>
       </c>
-      <c r="H55" s="35" t="n"/>
+      <c r="H55" s="37" t="n"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -36192,7 +36193,7 @@
       <c r="G56" s="36" t="n">
         <v>0.8208333333333333</v>
       </c>
-      <c r="H56" s="35" t="n"/>
+      <c r="H56" s="37" t="n"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -36224,7 +36225,7 @@
       <c r="G57" s="36" t="n">
         <v>0.8166666666666667</v>
       </c>
-      <c r="H57" s="35" t="n"/>
+      <c r="H57" s="37" t="n"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -36256,7 +36257,7 @@
       <c r="G58" s="36" t="n">
         <v>0.8173611111111111</v>
       </c>
-      <c r="H58" s="35" t="n"/>
+      <c r="H58" s="37" t="n"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -36288,7 +36289,7 @@
       <c r="G59" s="36" t="n">
         <v>0.8138888888888889</v>
       </c>
-      <c r="H59" s="35" t="n"/>
+      <c r="H59" s="37" t="n"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -36320,7 +36321,7 @@
       <c r="G60" s="36" t="n">
         <v>0.9402777777777778</v>
       </c>
-      <c r="H60" s="35" t="n"/>
+      <c r="H60" s="37" t="n"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -36352,7 +36353,7 @@
       <c r="G61" s="36" t="n">
         <v>0.81875</v>
       </c>
-      <c r="H61" s="35" t="n"/>
+      <c r="H61" s="37" t="n"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -36384,7 +36385,7 @@
       <c r="G62" s="36" t="n">
         <v>0.8118055555555556</v>
       </c>
-      <c r="H62" s="35" t="n"/>
+      <c r="H62" s="37" t="n"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -36416,7 +36417,7 @@
       <c r="G63" s="36" t="n">
         <v>0.81875</v>
       </c>
-      <c r="H63" s="35" t="n"/>
+      <c r="H63" s="37" t="n"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -36448,7 +36449,7 @@
       <c r="G64" s="36" t="n">
         <v>0.85</v>
       </c>
-      <c r="H64" s="35" t="n"/>
+      <c r="H64" s="37" t="n"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -36480,7 +36481,7 @@
       <c r="G65" s="36" t="n">
         <v>0.6527777777777778</v>
       </c>
-      <c r="H65" s="35" t="n"/>
+      <c r="H65" s="37" t="n"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -36512,7 +36513,7 @@
       <c r="G66" s="36" t="n">
         <v>0.65</v>
       </c>
-      <c r="H66" s="35" t="n"/>
+      <c r="H66" s="37" t="n"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -36544,7 +36545,7 @@
       <c r="G67" s="36" t="n">
         <v>0.8756944444444444</v>
       </c>
-      <c r="H67" s="35" t="n"/>
+      <c r="H67" s="37" t="n"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -36576,7 +36577,7 @@
       <c r="G68" s="36" t="n">
         <v>0.9958333333333333</v>
       </c>
-      <c r="H68" s="35" t="n"/>
+      <c r="H68" s="37" t="n"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -36608,7 +36609,7 @@
       <c r="G69" s="36" t="n">
         <v>0.3430555555555556</v>
       </c>
-      <c r="H69" s="35" t="n"/>
+      <c r="H69" s="37" t="n"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -36640,7 +36641,7 @@
       <c r="G70" s="36" t="n">
         <v>0.3236111111111111</v>
       </c>
-      <c r="H70" s="35" t="n"/>
+      <c r="H70" s="37" t="n"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -36672,7 +36673,7 @@
       <c r="G71" s="36" t="n">
         <v>0.3173611111111111</v>
       </c>
-      <c r="H71" s="35" t="n"/>
+      <c r="H71" s="37" t="n"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -36704,7 +36705,7 @@
       <c r="G72" s="36" t="n">
         <v>0.3138888888888889</v>
       </c>
-      <c r="H72" s="35" t="n"/>
+      <c r="H72" s="37" t="n"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -36736,7 +36737,7 @@
       <c r="G73" s="36" t="n">
         <v>0.3152777777777778</v>
       </c>
-      <c r="H73" s="35" t="n"/>
+      <c r="H73" s="37" t="n"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -36768,7 +36769,7 @@
       <c r="G74" s="36" t="n">
         <v>0.3208333333333334</v>
       </c>
-      <c r="H74" s="35" t="n"/>
+      <c r="H74" s="37" t="n"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -36800,7 +36801,7 @@
       <c r="G75" s="36" t="n">
         <v>0.3083333333333333</v>
       </c>
-      <c r="H75" s="35" t="n"/>
+      <c r="H75" s="37" t="n"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -36832,7 +36833,7 @@
       <c r="G76" s="36" t="n">
         <v>0.3194444444444444</v>
       </c>
-      <c r="H76" s="35" t="n"/>
+      <c r="H76" s="37" t="n"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -36864,7 +36865,7 @@
       <c r="G77" s="36" t="n">
         <v>0.3256944444444445</v>
       </c>
-      <c r="H77" s="35" t="n"/>
+      <c r="H77" s="37" t="n"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -36896,7 +36897,7 @@
       <c r="G78" s="36" t="n">
         <v>0.3152777777777778</v>
       </c>
-      <c r="H78" s="35" t="n"/>
+      <c r="H78" s="37" t="n"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -36928,7 +36929,7 @@
       <c r="G79" s="36" t="n">
         <v>0.31875</v>
       </c>
-      <c r="H79" s="35" t="n"/>
+      <c r="H79" s="37" t="n"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -36960,7 +36961,7 @@
       <c r="G80" s="36" t="n">
         <v>0.3166666666666667</v>
       </c>
-      <c r="H80" s="35" t="n"/>
+      <c r="H80" s="37" t="n"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -36992,7 +36993,7 @@
       <c r="G81" s="36" t="n">
         <v>0.3131944444444444</v>
       </c>
-      <c r="H81" s="35" t="n"/>
+      <c r="H81" s="37" t="n"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -37024,7 +37025,7 @@
       <c r="G82" s="36" t="n">
         <v>0.8138888888888889</v>
       </c>
-      <c r="H82" s="35" t="n"/>
+      <c r="H82" s="37" t="n"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -37056,7 +37057,7 @@
       <c r="G83" s="36" t="n">
         <v>0.81875</v>
       </c>
-      <c r="H83" s="35" t="n"/>
+      <c r="H83" s="37" t="n"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -37088,7 +37089,7 @@
       <c r="G84" s="36" t="n">
         <v>0.8090277777777778</v>
       </c>
-      <c r="H84" s="35" t="n"/>
+      <c r="H84" s="37" t="n"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -37120,7 +37121,7 @@
       <c r="G85" s="36" t="n">
         <v>0.8236111111111111</v>
       </c>
-      <c r="H85" s="35" t="n"/>
+      <c r="H85" s="37" t="n"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -37152,7 +37153,7 @@
       <c r="G86" s="36" t="n">
         <v>0.8145833333333333</v>
       </c>
-      <c r="H86" s="35" t="n"/>
+      <c r="H86" s="37" t="n"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -37184,7 +37185,7 @@
       <c r="G87" s="36" t="n">
         <v>0.8215277777777777</v>
       </c>
-      <c r="H87" s="35" t="n"/>
+      <c r="H87" s="37" t="n"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -37216,7 +37217,7 @@
       <c r="G88" s="36" t="n">
         <v>0.8152777777777778</v>
       </c>
-      <c r="H88" s="35" t="n"/>
+      <c r="H88" s="37" t="n"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -37248,7 +37249,7 @@
       <c r="G89" s="36" t="n">
         <v>0.8090277777777778</v>
       </c>
-      <c r="H89" s="35" t="n"/>
+      <c r="H89" s="37" t="n"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -37280,7 +37281,7 @@
       <c r="G90" s="36" t="n">
         <v>0.8125</v>
       </c>
-      <c r="H90" s="35" t="n"/>
+      <c r="H90" s="37" t="n"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -37312,7 +37313,7 @@
       <c r="G91" s="36" t="n">
         <v>0.88125</v>
       </c>
-      <c r="H91" s="35" t="n"/>
+      <c r="H91" s="37" t="n"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -37344,7 +37345,7 @@
       <c r="G92" s="36" t="n">
         <v>0.8083333333333333</v>
       </c>
-      <c r="H92" s="35" t="n"/>
+      <c r="H92" s="37" t="n"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -37376,7 +37377,7 @@
       <c r="G93" s="36" t="n">
         <v>0.6402777777777777</v>
       </c>
-      <c r="H93" s="35" t="n"/>
+      <c r="H93" s="37" t="n"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -37408,7 +37409,7 @@
       <c r="G94" s="36" t="n">
         <v>0.6479166666666667</v>
       </c>
-      <c r="H94" s="35" t="n"/>
+      <c r="H94" s="37" t="n"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -37440,7 +37441,7 @@
       <c r="G95" s="36" t="n">
         <v>0.9826388888888888</v>
       </c>
-      <c r="H95" s="35" t="n"/>
+      <c r="H95" s="37" t="n"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -37472,7 +37473,7 @@
       <c r="G96" s="36" t="n">
         <v>0.3180555555555555</v>
       </c>
-      <c r="H96" s="35" t="n"/>
+      <c r="H96" s="37" t="n"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -37504,7 +37505,7 @@
       <c r="G97" s="36" t="n">
         <v>0.3159722222222222</v>
       </c>
-      <c r="H97" s="35" t="n"/>
+      <c r="H97" s="37" t="n"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -37536,7 +37537,7 @@
       <c r="G98" s="36" t="n">
         <v>0.3173611111111111</v>
       </c>
-      <c r="H98" s="35" t="n"/>
+      <c r="H98" s="37" t="n"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -37568,7 +37569,7 @@
       <c r="G99" s="36" t="n">
         <v>0.3180555555555555</v>
       </c>
-      <c r="H99" s="35" t="n"/>
+      <c r="H99" s="37" t="n"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -37600,7 +37601,7 @@
       <c r="G100" s="36" t="n">
         <v>0.3229166666666667</v>
       </c>
-      <c r="H100" s="35" t="n"/>
+      <c r="H100" s="37" t="n"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -37632,7 +37633,7 @@
       <c r="G101" s="36" t="n">
         <v>0.3236111111111111</v>
       </c>
-      <c r="H101" s="35" t="n"/>
+      <c r="H101" s="37" t="n"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -37664,7 +37665,7 @@
       <c r="G102" s="36" t="n">
         <v>0.3152777777777778</v>
       </c>
-      <c r="H102" s="35" t="n"/>
+      <c r="H102" s="37" t="n"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -37696,7 +37697,7 @@
       <c r="G103" s="36" t="n">
         <v>0.8152777777777778</v>
       </c>
-      <c r="H103" s="35" t="n"/>
+      <c r="H103" s="37" t="n"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -37728,7 +37729,7 @@
       <c r="G104" s="36" t="n">
         <v>0.8215277777777777</v>
       </c>
-      <c r="H104" s="35" t="n"/>
+      <c r="H104" s="37" t="n"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -37760,7 +37761,7 @@
       <c r="G105" s="36" t="n">
         <v>0.8840277777777777</v>
       </c>
-      <c r="H105" s="35" t="n"/>
+      <c r="H105" s="37" t="n"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -37792,7 +37793,7 @@
       <c r="G106" s="36" t="n">
         <v>0.8277777777777777</v>
       </c>
-      <c r="H106" s="35" t="n"/>
+      <c r="H106" s="37" t="n"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -37824,7 +37825,7 @@
       <c r="G107" s="36" t="n">
         <v>0.8159722222222222</v>
       </c>
-      <c r="H107" s="35" t="n"/>
+      <c r="H107" s="37" t="n"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -37856,7 +37857,7 @@
       <c r="G108" s="36" t="n">
         <v>0.8194444444444444</v>
       </c>
-      <c r="H108" s="35" t="n"/>
+      <c r="H108" s="37" t="n"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -37888,7 +37889,7 @@
       <c r="G109" s="36" t="n">
         <v>0.8131944444444444</v>
       </c>
-      <c r="H109" s="35" t="n"/>
+      <c r="H109" s="37" t="n"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -37920,7 +37921,7 @@
       <c r="G110" s="36" t="n">
         <v>0.8215277777777777</v>
       </c>
-      <c r="H110" s="35" t="n"/>
+      <c r="H110" s="37" t="n"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -37952,7 +37953,7 @@
       <c r="G111" s="36" t="n">
         <v>0.8111111111111111</v>
       </c>
-      <c r="H111" s="35" t="n"/>
+      <c r="H111" s="37" t="n"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -37984,7 +37985,7 @@
       <c r="G112" s="36" t="n">
         <v>0.8340277777777778</v>
       </c>
-      <c r="H112" s="35" t="n"/>
+      <c r="H112" s="37" t="n"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -38016,7 +38017,7 @@
       <c r="G113" s="36" t="n">
         <v>0.8201388888888889</v>
       </c>
-      <c r="H113" s="35" t="n"/>
+      <c r="H113" s="37" t="n"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -38048,7 +38049,7 @@
       <c r="G114" s="36" t="n">
         <v>0.8194444444444444</v>
       </c>
-      <c r="H114" s="35" t="n"/>
+      <c r="H114" s="37" t="n"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -38080,7 +38081,7 @@
       <c r="G115" s="36" t="n">
         <v>0.8236111111111111</v>
       </c>
-      <c r="H115" s="35" t="n"/>
+      <c r="H115" s="37" t="n"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -38112,7 +38113,7 @@
       <c r="G116" s="36" t="n">
         <v>0.8236111111111111</v>
       </c>
-      <c r="H116" s="35" t="n"/>
+      <c r="H116" s="37" t="n"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -38144,7 +38145,7 @@
       <c r="G117" s="36" t="n">
         <v>0.8090277777777778</v>
       </c>
-      <c r="H117" s="35" t="n"/>
+      <c r="H117" s="37" t="n"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -38176,7 +38177,7 @@
       <c r="G118" s="36" t="n">
         <v>0.6583333333333333</v>
       </c>
-      <c r="H118" s="35" t="n"/>
+      <c r="H118" s="37" t="n"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -38208,7 +38209,7 @@
       <c r="G119" s="36" t="n">
         <v>0.6423611111111112</v>
       </c>
-      <c r="H119" s="35" t="n"/>
+      <c r="H119" s="37" t="n"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -38240,7 +38241,7 @@
       <c r="G120" s="36" t="n">
         <v>0.8375</v>
       </c>
-      <c r="H120" s="35" t="n"/>
+      <c r="H120" s="37" t="n"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -38272,7 +38273,7 @@
       <c r="G121" s="36" t="n">
         <v>0.9868055555555556</v>
       </c>
-      <c r="H121" s="35" t="n"/>
+      <c r="H121" s="37" t="n"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -38304,7 +38305,7 @@
       <c r="G122" s="36" t="n">
         <v>0.3152777777777778</v>
       </c>
-      <c r="H122" s="35" t="n"/>
+      <c r="H122" s="37" t="n"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -38336,7 +38337,7 @@
       <c r="G123" s="36" t="n">
         <v>0.3368055555555556</v>
       </c>
-      <c r="H123" s="35" t="n"/>
+      <c r="H123" s="37" t="n"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -38368,7 +38369,7 @@
       <c r="G124" s="36" t="n">
         <v>0.3145833333333333</v>
       </c>
-      <c r="H124" s="35" t="n"/>
+      <c r="H124" s="37" t="n"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -38400,7 +38401,7 @@
       <c r="G125" s="36" t="n">
         <v>0.3138888888888889</v>
       </c>
-      <c r="H125" s="35" t="n"/>
+      <c r="H125" s="37" t="n"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -38432,7 +38433,7 @@
       <c r="G126" s="36" t="n">
         <v>0.3166666666666667</v>
       </c>
-      <c r="H126" s="35" t="n"/>
+      <c r="H126" s="37" t="n"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -38464,7 +38465,7 @@
       <c r="G127" s="36" t="n">
         <v>0.3166666666666667</v>
       </c>
-      <c r="H127" s="35" t="n"/>
+      <c r="H127" s="37" t="n"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -38496,7 +38497,7 @@
       <c r="G128" s="36" t="n">
         <v>0.3131944444444444</v>
       </c>
-      <c r="H128" s="35" t="n"/>
+      <c r="H128" s="37" t="n"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -38528,7 +38529,7 @@
       <c r="G129" s="36" t="n">
         <v>0.4638888888888889</v>
       </c>
-      <c r="H129" s="35" t="n"/>
+      <c r="H129" s="37" t="n"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -38560,7 +38561,7 @@
       <c r="G130" s="36" t="n">
         <v>0.3263888888888889</v>
       </c>
-      <c r="H130" s="35" t="n"/>
+      <c r="H130" s="37" t="n"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -38592,7 +38593,7 @@
       <c r="G131" s="36" t="n">
         <v>0.8479166666666667</v>
       </c>
-      <c r="H131" s="35" t="n"/>
+      <c r="H131" s="37" t="n"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -38624,7 +38625,7 @@
       <c r="G132" s="36" t="n">
         <v>0.8215277777777777</v>
       </c>
-      <c r="H132" s="35" t="n"/>
+      <c r="H132" s="37" t="n"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -38656,7 +38657,7 @@
       <c r="G133" s="36" t="n">
         <v>0.8083333333333333</v>
       </c>
-      <c r="H133" s="35" t="n"/>
+      <c r="H133" s="37" t="n"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -38688,7 +38689,7 @@
       <c r="G134" s="36" t="n">
         <v>0.8583333333333333</v>
       </c>
-      <c r="H134" s="35" t="n"/>
+      <c r="H134" s="37" t="n"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -38720,7 +38721,7 @@
       <c r="G135" s="36" t="n">
         <v>0.8076388888888889</v>
       </c>
-      <c r="H135" s="35" t="n"/>
+      <c r="H135" s="37" t="n"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -38752,7 +38753,7 @@
       <c r="G136" s="36" t="n">
         <v>0.8083333333333333</v>
       </c>
-      <c r="H136" s="35" t="n"/>
+      <c r="H136" s="37" t="n"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -38784,7 +38785,7 @@
       <c r="G137" s="36" t="n">
         <v>0.8083333333333333</v>
       </c>
-      <c r="H137" s="35" t="n"/>
+      <c r="H137" s="37" t="n"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -38816,7 +38817,7 @@
       <c r="G138" s="36" t="n">
         <v>0.8166666666666667</v>
       </c>
-      <c r="H138" s="35" t="n"/>
+      <c r="H138" s="37" t="n"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -38848,7 +38849,7 @@
       <c r="G139" s="36" t="n">
         <v>0.8180555555555555</v>
       </c>
-      <c r="H139" s="35" t="n"/>
+      <c r="H139" s="37" t="n"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -38880,7 +38881,7 @@
       <c r="G140" s="36" t="n">
         <v>0.8118055555555556</v>
       </c>
-      <c r="H140" s="35" t="n"/>
+      <c r="H140" s="37" t="n"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -38912,7 +38913,7 @@
       <c r="G141" s="36" t="n">
         <v>0.8145833333333333</v>
       </c>
-      <c r="H141" s="35" t="n"/>
+      <c r="H141" s="37" t="n"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -38944,7 +38945,7 @@
       <c r="G142" s="36" t="n">
         <v>0.8166666666666667</v>
       </c>
-      <c r="H142" s="35" t="n"/>
+      <c r="H142" s="37" t="n"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -38976,7 +38977,7 @@
       <c r="G143" s="36" t="n">
         <v>0.6486111111111111</v>
       </c>
-      <c r="H143" s="35" t="n"/>
+      <c r="H143" s="37" t="n"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -39008,7 +39009,7 @@
       <c r="G144" s="36" t="n">
         <v>0.6465277777777778</v>
       </c>
-      <c r="H144" s="35" t="n"/>
+      <c r="H144" s="37" t="n"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -39040,7 +39041,7 @@
       <c r="G145" s="36" t="n">
         <v>0.6513888888888889</v>
       </c>
-      <c r="H145" s="35" t="n"/>
+      <c r="H145" s="37" t="n"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -39072,7 +39073,7 @@
       <c r="G146" s="36" t="n">
         <v>0.8486111111111111</v>
       </c>
-      <c r="H146" s="35" t="n"/>
+      <c r="H146" s="37" t="n"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -39104,7 +39105,7 @@
       <c r="G147" s="36" t="n">
         <v>0.3138888888888889</v>
       </c>
-      <c r="H147" s="35" t="n"/>
+      <c r="H147" s="37" t="n"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -39136,7 +39137,7 @@
       <c r="G148" s="36" t="n">
         <v>0.3194444444444444</v>
       </c>
-      <c r="H148" s="35" t="n"/>
+      <c r="H148" s="37" t="n"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -39168,7 +39169,7 @@
       <c r="G149" s="36" t="n">
         <v>0.3159722222222222</v>
       </c>
-      <c r="H149" s="35" t="n"/>
+      <c r="H149" s="37" t="n"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -39200,7 +39201,7 @@
       <c r="G150" s="36" t="n">
         <v>0.3131944444444444</v>
       </c>
-      <c r="H150" s="35" t="n"/>
+      <c r="H150" s="37" t="n"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -39232,7 +39233,7 @@
       <c r="G151" s="36" t="n">
         <v>0.3180555555555555</v>
       </c>
-      <c r="H151" s="35" t="n"/>
+      <c r="H151" s="37" t="n"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -39264,7 +39265,7 @@
       <c r="G152" s="36" t="n">
         <v>0.3180555555555555</v>
       </c>
-      <c r="H152" s="35" t="n"/>
+      <c r="H152" s="37" t="n"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -39296,7 +39297,7 @@
       <c r="G153" s="36" t="n">
         <v>0.3173611111111111</v>
       </c>
-      <c r="H153" s="35" t="n"/>
+      <c r="H153" s="37" t="n"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -39328,7 +39329,7 @@
       <c r="G154" s="36" t="n">
         <v>0.3194444444444444</v>
       </c>
-      <c r="H154" s="35" t="n"/>
+      <c r="H154" s="37" t="n"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -39360,7 +39361,7 @@
       <c r="G155" s="36" t="n">
         <v>0.3270833333333333</v>
       </c>
-      <c r="H155" s="35" t="n"/>
+      <c r="H155" s="37" t="n"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -39392,7 +39393,7 @@
       <c r="G156" s="36" t="n">
         <v>0.3138888888888889</v>
       </c>
-      <c r="H156" s="35" t="n"/>
+      <c r="H156" s="37" t="n"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -39424,7 +39425,7 @@
       <c r="G157" s="36" t="n">
         <v>0.3180555555555555</v>
       </c>
-      <c r="H157" s="35" t="n"/>
+      <c r="H157" s="37" t="n"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -39456,7 +39457,7 @@
       <c r="G158" s="36" t="n">
         <v>0.8125</v>
       </c>
-      <c r="H158" s="35" t="n"/>
+      <c r="H158" s="37" t="n"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -39488,7 +39489,7 @@
       <c r="G159" s="36" t="n">
         <v>0.8152777777777778</v>
       </c>
-      <c r="H159" s="35" t="n"/>
+      <c r="H159" s="37" t="n"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -39520,7 +39521,7 @@
       <c r="G160" s="36" t="n">
         <v>0.8201388888888889</v>
       </c>
-      <c r="H160" s="35" t="n"/>
+      <c r="H160" s="37" t="n"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -39552,7 +39553,7 @@
       <c r="G161" s="36" t="n">
         <v>0.81875</v>
       </c>
-      <c r="H161" s="35" t="n"/>
+      <c r="H161" s="37" t="n"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -39584,7 +39585,7 @@
       <c r="G162" s="36" t="n">
         <v>0.8118055555555556</v>
       </c>
-      <c r="H162" s="35" t="n"/>
+      <c r="H162" s="37" t="n"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -39616,7 +39617,7 @@
       <c r="G163" s="36" t="n">
         <v>0.8180555555555555</v>
       </c>
-      <c r="H163" s="35" t="n"/>
+      <c r="H163" s="37" t="n"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -39648,7 +39649,7 @@
       <c r="G164" s="36" t="n">
         <v>0.8152777777777778</v>
       </c>
-      <c r="H164" s="35" t="n"/>
+      <c r="H164" s="37" t="n"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -39680,7 +39681,7 @@
       <c r="G165" s="36" t="n">
         <v>0.8145833333333333</v>
       </c>
-      <c r="H165" s="35" t="n"/>
+      <c r="H165" s="37" t="n"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -39712,7 +39713,7 @@
       <c r="G166" s="36" t="n">
         <v>0.8145833333333333</v>
       </c>
-      <c r="H166" s="35" t="n"/>
+      <c r="H166" s="37" t="n"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -39744,7 +39745,7 @@
       <c r="G167" s="36" t="n">
         <v>0.8243055555555555</v>
       </c>
-      <c r="H167" s="35" t="n"/>
+      <c r="H167" s="37" t="n"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -39776,7 +39777,7 @@
       <c r="G168" s="36" t="n">
         <v>0.8131944444444444</v>
       </c>
-      <c r="H168" s="35" t="n"/>
+      <c r="H168" s="37" t="n"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -39808,7 +39809,7 @@
       <c r="G169" s="36" t="n">
         <v>0.8118055555555556</v>
       </c>
-      <c r="H169" s="35" t="n"/>
+      <c r="H169" s="37" t="n"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -39840,7 +39841,7 @@
       <c r="G170" s="36" t="n">
         <v>0.8368055555555556</v>
       </c>
-      <c r="H170" s="35" t="n"/>
+      <c r="H170" s="37" t="n"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -39872,7 +39873,7 @@
       <c r="G171" s="36" t="n">
         <v>0.8125</v>
       </c>
-      <c r="H171" s="35" t="n"/>
+      <c r="H171" s="37" t="n"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -39904,7 +39905,7 @@
       <c r="G172" s="36" t="n">
         <v>0.8381944444444445</v>
       </c>
-      <c r="H172" s="35" t="n"/>
+      <c r="H172" s="37" t="n"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -39936,7 +39937,7 @@
       <c r="G173" s="36" t="n">
         <v>0.8159722222222222</v>
       </c>
-      <c r="H173" s="35" t="n"/>
+      <c r="H173" s="37" t="n"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -39968,7 +39969,7 @@
       <c r="G174" s="36" t="n">
         <v>0.8215277777777777</v>
       </c>
-      <c r="H174" s="35" t="n"/>
+      <c r="H174" s="37" t="n"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -40000,7 +40001,7 @@
       <c r="G175" s="36" t="n">
         <v>0.8104166666666667</v>
       </c>
-      <c r="H175" s="35" t="n"/>
+      <c r="H175" s="37" t="n"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -40032,7 +40033,7 @@
       <c r="G176" s="36" t="n">
         <v>0.8194444444444444</v>
       </c>
-      <c r="H176" s="35" t="n"/>
+      <c r="H176" s="37" t="n"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -40064,7 +40065,7 @@
       <c r="G177" s="36" t="n">
         <v>0.6409722222222223</v>
       </c>
-      <c r="H177" s="35" t="n"/>
+      <c r="H177" s="37" t="n"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -40096,7 +40097,7 @@
       <c r="G178" s="36" t="n">
         <v>0.30625</v>
       </c>
-      <c r="H178" s="35" t="n"/>
+      <c r="H178" s="37" t="n"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -40128,7 +40129,7 @@
       <c r="G179" s="36" t="n">
         <v>0.3166666666666667</v>
       </c>
-      <c r="H179" s="35" t="n"/>
+      <c r="H179" s="37" t="n"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -40160,7 +40161,7 @@
       <c r="G180" s="36" t="n">
         <v>0.3222222222222222</v>
       </c>
-      <c r="H180" s="35" t="n"/>
+      <c r="H180" s="37" t="n"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -40192,7 +40193,7 @@
       <c r="G181" s="36" t="n">
         <v>0.3090277777777778</v>
       </c>
-      <c r="H181" s="35" t="n"/>
+      <c r="H181" s="37" t="n"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -40224,7 +40225,7 @@
       <c r="G182" s="36" t="n">
         <v>0.3194444444444444</v>
       </c>
-      <c r="H182" s="35" t="n"/>
+      <c r="H182" s="37" t="n"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -40256,7 +40257,7 @@
       <c r="G183" s="36" t="n">
         <v>0.3159722222222222</v>
       </c>
-      <c r="H183" s="35" t="n"/>
+      <c r="H183" s="37" t="n"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -40288,7 +40289,7 @@
       <c r="G184" s="36" t="n">
         <v>0.3222222222222222</v>
       </c>
-      <c r="H184" s="35" t="n"/>
+      <c r="H184" s="37" t="n"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -40320,7 +40321,7 @@
       <c r="G185" s="36" t="n">
         <v>0.3111111111111111</v>
       </c>
-      <c r="H185" s="35" t="n"/>
+      <c r="H185" s="37" t="n"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -40352,7 +40353,7 @@
       <c r="G186" s="36" t="n">
         <v>0.3229166666666667</v>
       </c>
-      <c r="H186" s="35" t="n"/>
+      <c r="H186" s="37" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -40686,17 +40687,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="37" t="inlineStr">
+      <c r="A1" s="38" t="inlineStr">
         <is>
           <t>Setting</t>
         </is>
       </c>
-      <c r="B1" s="37" t="inlineStr">
+      <c r="B1" s="38" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C1" s="37" t="inlineStr">
+      <c r="C1" s="38" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -40713,7 +40714,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>The course's 'today' (the data is as of this date). Use this cell instead of TODAY() so your answers never change.</t>
+          <t>The course's 'today'. Use this cell instead of TODAY() so your answers never change.</t>
         </is>
       </c>
     </row>
@@ -40809,7 +40810,7 @@
           <t>INT strips the time from a date-time. Subtract the two dates</t>
         </is>
       </c>
-      <c r="D6" cm="1" s="38">
+      <c r="D6" cm="1" s="39">
         <f t="array" ref="D6">IF(COUNT('Stays'!$K$2:$K$370)=0,"",COUNTIF('Stays'!$K$2:$K$370,"&gt;=2"))</f>
         <v/>
       </c>
@@ -40856,7 +40857,7 @@
           <t>Use IF to pick the clock start for each row, then count midnights the same way as in B1</t>
         </is>
       </c>
-      <c r="D8" cm="1" s="38">
+      <c r="D8" cm="1" s="39">
         <f t="array" ref="D8">IF(COUNT('Stays'!$L$2:$L$370)=0,"",COUNTIF('Stays'!$L$2:$L$370,"&gt;=2"))</f>
         <v/>
       </c>
@@ -40873,7 +40874,7 @@
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>Fill the AdmitDay column with the weekday name of each AdmitDateTime (Monday, Tuesday, …). What was the average length of stay, in HOURS, for patients admitted on a Friday? Round to 1 decimal place.</t>
+          <t>Fill the AdmitDay column with the weekday name of each AdmitDateTime (Monday, Tuesday, …). Start in M2. What was the average length of stay, in HOURS, for patients admitted on a Friday? Use your LOSDays column and round to 1 decimal place.</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -40881,7 +40882,7 @@
           <t>TEXT(date, "dddd") gives the weekday name. AVERAGEIF (a preview of Lesson 2.5) or AVERAGE(IF(…)) averages the Friday rows</t>
         </is>
       </c>
-      <c r="D9" s="39" t="n"/>
+      <c r="D9" s="40" t="n"/>
       <c r="E9" s="22">
         <f>IF(IFERROR(D9="",FALSE),"",IF(IFERROR(AND(ISNUMBER(D9),OR(ABS(D9-'Bonus Key'!$C$8)&lt;=0.051)),FALSE),"✔ Correct","✘ Not yet"))</f>
         <v/>
@@ -40903,7 +40904,7 @@
           <t>Build a small seven-row table of averages, one per weekday</t>
         </is>
       </c>
-      <c r="D10" s="40" t="n"/>
+      <c r="D10" s="41" t="n"/>
       <c r="E10" s="22">
         <f>IF(IFERROR(D10="",FALSE),"",IF(IFERROR(OR(LOWER(TRIM(D10&amp;""))=LOWER(TRIM('Bonus Key'!$C$9&amp;"")),LOWER(TRIM(D10&amp;""))="thu"),FALSE),"✔ Correct","✘ Not yet"))</f>
         <v/>

--- a/02-formulas-functions/03-date-time-functions/2.3-date-time-functions.xlsx
+++ b/02-formulas-functions/03-date-time-functions/2.3-date-time-functions.xlsx
@@ -217,7 +217,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -320,37 +320,34 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="170" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="171" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="171" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -944,7 +941,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="33" customHeight="1">
+    <row r="15" ht="18" customHeight="1">
       <c r="B15" s="8" t="inlineStr">
         <is>
           <t>3. Check yourself</t>
@@ -952,7 +949,7 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>The Check column shows ✔ Correct (green) or ✘ Not yet (red). Tasks marked 'See key' are checked by comparing with the answer key.</t>
+          <t>The Check column shows ✔ Correct (green) or ✘ Not yet (red).</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1029,7 @@
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Pre-filled summary formula — it reads the work you did on another sheet.</t>
+          <t>Pre-filled summary formula. It reads the work you did on another sheet, so don't type over it.</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1053,7 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Not matching yet — check the hint and try again.</t>
+          <t>Not matching yet. Check the hint and try again.</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1073,7 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Data: 369 rows — Excel Table 'tblStays'</t>
+          <t>Data: 369 rows, in the Excel Table 'tblStays'</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1085,7 @@
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>Data: 369 rows — Excel Table 'tblClaims'</t>
+          <t>Data: 369 rows, in the Excel Table 'tblClaims'</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1097,7 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Data: 226 rows — Excel Table 'tblED'</t>
+          <t>Data: 226 rows, in the Excel Table 'tblED'</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1109,7 @@
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Data: 185 rows — Excel Table 'tblShifts'</t>
+          <t>Data: 185 rows, in the Excel Table 'tblShifts'</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1121,7 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Data: 18 rows — Excel Table 'tblHolidays'</t>
+          <t>Data: 18 rows, in the Excel Table 'tblHolidays'</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1133,7 @@
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Data: 1 rows</t>
+          <t>Data: 1 row</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1181,7 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -1198,7 +1195,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="43" t="inlineStr">
         <is>
-          <t>Spoiler alert — try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution; column E is that same formula, live, proving it works.</t>
+          <t>Spoiler alert: try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution, and column E recalculates a formula for it live, proving the answer.</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1366,7 @@
           <t>=SUMPRODUCT(--(WEEKDAY(Stays!G2:G370,2)&gt;5))</t>
         </is>
       </c>
-      <c r="E9" cm="1" s="53">
+      <c r="E9" cm="1" s="19">
         <f t="array" ref="E9">SUMPRODUCT(--(WEEKDAY(Stays!G2:G370,2)&gt;5))</f>
         <v/>
       </c>
@@ -1398,13 +1395,13 @@
           <t>=SUMPRODUCT((Stays!G2:G370&gt;=DATE(2025,4,1))*(Stays!G2:G370&lt;DATE(2025,5,1)))</t>
         </is>
       </c>
-      <c r="E10" cm="1" s="53">
+      <c r="E10" cm="1" s="19">
         <f t="array" ref="E10">SUMPRODUCT((Stays!G2:G370&gt;=DATE(2025,4,1))*(Stays!G2:G370&lt;DATE(2025,5,1)))</f>
         <v/>
       </c>
       <c r="F10" s="19" t="inlineStr">
         <is>
-          <t>DATE(2025,4,1) builds the serial number for April 1, and multiplying the two TRUE/FALSE lists keeps only rows that pass both tests (AND logic). The upper bound is before May 1, not on or before April 30. AdmitDateTime includes a time, so 04/30/2025 19:59 is *greater* than DATE(2025,4,30), which means midnight. &lt;=DATE(2025,4,30) would miss the 3 admissions on April 30 and return 24. =SUMPRODUCT((MONTH(Stays!G2:G370)=4)*(YEAR(Stays!G2:G370)=2025)) also works.</t>
+          <t>DATE(2025,4,1) builds the serial number for April 1, and multiplying the two TRUE/FALSE lists keeps only rows that pass both tests (AND logic). The upper bound is before May 1, not on or before April 30. AdmitDateTime includes a time, so 04/30/2025 19:59 is greater than DATE(2025,4,30), which means midnight. &lt;=DATE(2025,4,30) would miss the 3 admissions on April 30 and return 24. =SUMPRODUCT((MONTH(Stays!G2:G370)=4)*(YEAR(Stays!G2:G370)=2025)) also works.</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1474,7 @@
           <t>Fill the yellow DaysToPay column on the Claims sheet with the calendar days from SubmitDate to PaidDate. 94 claims have no PaidDate yet, so make those rows return "" (empty text). Start in H2. The gray cell averages your column. What is the average days to pay?</t>
         </is>
       </c>
-      <c r="C13" s="54" t="n">
+      <c r="C13" s="53" t="n">
         <v>27.62181818181818</v>
       </c>
       <c r="D13" s="46" t="inlineStr">
@@ -1485,7 +1482,7 @@
           <t>=IF(G2="","",G2-F2)</t>
         </is>
       </c>
-      <c r="E13" cm="1" s="55">
+      <c r="E13" cm="1" s="54">
         <f t="array" ref="E13">SUMPRODUCT((Claims!G2:G370&lt;&gt;"")*(Claims!G2:G370-Claims!F2:F370))/COUNT(Claims!G2:G370)</f>
         <v/>
       </c>
@@ -1514,7 +1511,7 @@
           <t>=NETWORKDAYS(Claims!F307,Settings!$B$2,Holidays!$A$2:$A$19)</t>
         </is>
       </c>
-      <c r="E14" cm="1" s="53">
+      <c r="E14" cm="1" s="19">
         <f t="array" ref="E14">NETWORKDAYS(Claims!F307,Settings!$B$2,Holidays!$A$2:$A$19)</f>
         <v/>
       </c>
@@ -1564,7 +1561,7 @@
           <t>Fill the yellow DoorToProviderMin column on the ED sheet with the minutes from ArrivalDateTime to ProviderSeenDateTime. 9 patients left without being seen and have no ProviderSeenDateTime, so make those rows return "". Start in H2. The gray cell averages your column. What is the average door-to-provider time in minutes?</t>
         </is>
       </c>
-      <c r="C16" s="54" t="n">
+      <c r="C16" s="53" t="n">
         <v>49.14746543778802</v>
       </c>
       <c r="D16" s="46" t="inlineStr">
@@ -1572,13 +1569,13 @@
           <t>=IF(E2="","",(E2-C2)*1440)</t>
         </is>
       </c>
-      <c r="E16" cm="1" s="55">
+      <c r="E16" cm="1" s="54">
         <f t="array" ref="E16">SUMPRODUCT((ED!E2:E227&lt;&gt;"")*(ED!E2:E227-ED!C2:C227))*1440/COUNT(ED!E2:E227)</f>
         <v/>
       </c>
       <c r="F16" s="19" t="inlineStr">
         <is>
-          <t>Subtracting gives a fraction of a day (0.0347 is 50 minutes), and multiplying by 1,440 converts days to minutes. Because these columns hold the full date *and* time, visit ED211281 (arrived 23:51, seen at 00:03 the next morning) still gives a positive 12 minutes, with no special handling. The IF keeps LWBS visits out of the average instead of counting them as huge negative waits.</t>
+          <t>Subtracting gives a fraction of a day (0.0347 is 50 minutes), and multiplying by 1,440 converts days to minutes. Because these columns hold the full date and time, visit ED211281 (arrived 23:51, seen at 00:03 the next morning) still gives a positive 12 minutes, with no special handling. The IF keeps LWBS visits out of the average instead of counting them as huge negative waits.</t>
         </is>
       </c>
     </row>
@@ -1593,7 +1590,7 @@
           <t>The Shifts sheet's ClockIn and ClockOut columns hold clock times only, with no dates, and 69 shifts end after midnight. Fill the yellow PaidTime column with each shift's paid time: clock-out minus clock-in, corrected for shifts that cross midnight, minus a 30-minute unpaid meal break. Keep each result as a time value (don't multiply by 24). Start in H2. The gray cell totals your column in [h]:mm format. What is the total paid time for the week?</t>
         </is>
       </c>
-      <c r="C17" s="56" t="n">
+      <c r="C17" s="55" t="n">
         <v>92.24166666666666</v>
       </c>
       <c r="D17" s="46" t="inlineStr">
@@ -1601,13 +1598,13 @@
           <t>=MOD(G2-F2,1)-TIME(0,30,0)</t>
         </is>
       </c>
-      <c r="E17" cm="1" s="57">
+      <c r="E17" cm="1" s="56">
         <f t="array" ref="E17">SUMPRODUCT(MOD(Shifts!G2:G186-Shifts!F2:F186,1))-COUNT(Shifts!F2:F186)*TIME(0,30,0)</f>
         <v/>
       </c>
       <c r="F17" s="19" t="inlineStr">
         <is>
-          <t>Shift SH915484 clocked in at 18:48 and out at 08:20. 08:20 − 18:48 is negative (−0.4361 of a day). MOD(…, 1) adds one whole day to a negative result and leaves positive results alone, so the shift becomes 13:32. Subtract the meal break as a time, TIME(0,30,0) or "0:30" or 30/1440. Subtracting 0.5 would remove half a *day*. The total is 2,213.8 hours, so it needs [h]:mm. Plain h:mm would wrap past every 24 hours and show only the leftover hours. Without MOD the week totals 557.8 hours, because every overnight shift comes out negative. The PaidTime column is formatted h:mm, so a shift that comes out negative shows ######## instead of a time.</t>
+          <t>Shift SH915484 clocked in at 18:48 and out at 08:20. 08:20 − 18:48 is negative (−0.4361 of a day). MOD(…, 1) adds one whole day to a negative result and leaves positive results alone, so the shift becomes 13:32. Subtract the meal break as a time, TIME(0,30,0) or "0:30" or 30/1440. Subtracting 0.5 would remove half a day. The total is 2,213.8 hours, so it needs [h]:mm. Plain h:mm would wrap past every 24 hours and show only the leftover hours. Without MOD the week totals 557.8 hours, because every overnight shift comes out negative. The PaidTime column is formatted h:mm, so a shift that comes out negative shows ######## instead of a time.</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1631,7 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -1648,7 +1645,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="43" t="inlineStr">
         <is>
-          <t>Spoiler alert — try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution; column E is that same formula, live, proving it works.</t>
+          <t>Spoiler alert: try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution, and column E recalculates a formula for it live, proving the answer.</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1700,7 @@
           <t>=INT(H2)-INT(G2)</t>
         </is>
       </c>
-      <c r="E5" cm="1" s="53">
+      <c r="E5" cm="1" s="19">
         <f t="array" ref="E5">SUMPRODUCT(--((INT(Stays!H2:H370)-INT(Stays!G2:G370))&gt;=2))</f>
         <v/>
       </c>
@@ -1732,7 +1729,7 @@
           <t>=SUMPRODUCT((Stays!K2:K370&gt;=2)*(Stays!J2:J370&lt;2))</t>
         </is>
       </c>
-      <c r="E6" cm="1" s="53">
+      <c r="E6" cm="1" s="19">
         <f t="array" ref="E6">SUMPRODUCT(((INT(Stays!H2:H370)-INT(Stays!G2:G370))&gt;=2)*((Stays!H2:H370-Stays!G2:G370)&lt;2))</f>
         <v/>
       </c>
@@ -1761,7 +1758,7 @@
           <t>=INT(H2)-INT(IF(F2="",G2,F2))</t>
         </is>
       </c>
-      <c r="E7" cm="1" s="53">
+      <c r="E7" cm="1" s="19">
         <f t="array" ref="E7">SUMPRODUCT(--((INT(Stays!H2:H370)-(INT(Stays!G2:G370)*(Stays!F2:F370="")+INT(Stays!F2:F370)*(Stays!F2:F370&lt;&gt;"")))&gt;=2))</f>
         <v/>
       </c>
@@ -1782,7 +1779,7 @@
           <t>Fill the AdmitDay column with the weekday name of each AdmitDateTime (Monday, Tuesday, …). Start in M2. What was the average length of stay, in HOURS, for patients admitted on a Friday? Use your LOSDays column and round to 1 decimal place.</t>
         </is>
       </c>
-      <c r="C8" s="54" t="n">
+      <c r="C8" s="53" t="n">
         <v>108.3</v>
       </c>
       <c r="D8" s="46" t="inlineStr">
@@ -1790,7 +1787,7 @@
           <t>=ROUND(AVERAGEIF(Stays!M2:M370,"Friday",Stays!J2:J370)*24,1)</t>
         </is>
       </c>
-      <c r="E8" cm="1" s="55">
+      <c r="E8" cm="1" s="54">
         <f t="array" ref="E8">ROUND(SUMPRODUCT((WEEKDAY(Stays!G2:G370,2)=5)*(Stays!H2:H370-Stays!G2:G370))*24/SUMPRODUCT(--(WEEKDAY(Stays!G2:G370,2)=5)),1)</f>
         <v/>
       </c>
@@ -1819,8 +1816,8 @@
       <c r="D9" s="46" t="inlineStr">
         <is>
           <t>1. On the Bonus sheet, type Monday in G2 and drag the fill handle down to G8. AutoFill (Lesson 1.2) completes the week through Sunday.
-2. In H2, enter `=AVERAGEIF(Stays!$M$2:$M$370,G2,Stays!$J$2:$J$370)*24` and fill it down to H8.
-3. Find the largest average by eye, or let Excel find it: `=INDEX(G2:G8,MATCH(MAX(H2:H8),H2:H8,0))` (INDEX and MATCH are covered in Lesson 2.6).</t>
+2. In H2, enter =AVERAGEIF(Stays!$M$2:$M$370,G2,Stays!$J$2:$J$370)*24 and fill it down to H8.
+3. Find the largest average by eye, or let Excel find it: =INDEX(G2:G8,MATCH(MAX(H2:H8),H2:H8,0)) (INDEX and MATCH are covered in Lesson 2.6).</t>
         </is>
       </c>
       <c r="E9" s="18" t="inlineStr">
@@ -1975,7 +1972,7 @@
         </is>
       </c>
       <c r="D8" cm="1" s="24">
-        <f t="array" ref="D8">IF(COUNT('Stays'!$I$2:$I$370)=0,"",AVERAGE('Stays'!$I$2:$I$370))</f>
+        <f t="array" ref="D8">IF(COUNT(Stays!$I$2:$I$370)=0,"",AVERAGE(Stays!$I$2:$I$370))</f>
         <v/>
       </c>
       <c r="E8" s="22">
@@ -2066,7 +2063,7 @@
         </is>
       </c>
       <c r="D12" cm="1" s="24">
-        <f t="array" ref="D12">IF(COUNT('Stays'!$J$2:$J$370)=0,"",AVERAGE('Stays'!$J$2:$J$370))</f>
+        <f t="array" ref="D12">IF(COUNT(Stays!$J$2:$J$370)=0,"",AVERAGE(Stays!$J$2:$J$370))</f>
         <v/>
       </c>
       <c r="E12" s="22">
@@ -2113,7 +2110,7 @@
         </is>
       </c>
       <c r="D14" cm="1" s="27">
-        <f t="array" ref="D14">IF(COUNT('Claims'!$H$2:$H$370)=0,"",AVERAGE('Claims'!$H$2:$H$370))</f>
+        <f t="array" ref="D14">IF(COUNT(Claims!$H$2:$H$370)=0,"",AVERAGE(Claims!$H$2:$H$370))</f>
         <v/>
       </c>
       <c r="E14" s="22">
@@ -2182,7 +2179,7 @@
         </is>
       </c>
       <c r="D17" cm="1" s="27">
-        <f t="array" ref="D17">IF(COUNT('ED'!$H$2:$H$227)=0,"",AVERAGE('ED'!$H$2:$H$227))</f>
+        <f t="array" ref="D17">IF(COUNT(ED!$H$2:$H$227)=0,"",AVERAGE(ED!$H$2:$H$227))</f>
         <v/>
       </c>
       <c r="E17" s="22">
@@ -2207,7 +2204,7 @@
         </is>
       </c>
       <c r="D18" cm="1" s="28">
-        <f t="array" ref="D18">IF(COUNT('Shifts'!$H$2:$H$186)=0,"",SUM('Shifts'!$H$2:$H$186))</f>
+        <f t="array" ref="D18">IF(COUNT(Shifts!$H$2:$H$186)=0,"",SUM(Shifts!$H$2:$H$186))</f>
         <v/>
       </c>
       <c r="E18" s="22">
@@ -40747,7 +40744,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="79" customHeight="1">
+    <row r="2" ht="64" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Ashby Falls' utilization review nurse is preparing for a Medicare audit. Under the CMS two-midnight benchmark, an inpatient admission is generally expected to span at least two midnights of hospital care. This bonus uses a simplified, educational version (not billing guidance): count the midnights between two date-times by comparing their dates, not the hours between them. The nurse also wants to know whether the day of the week a patient is admitted affects how long they stay. Fill the yellow Midnights, BenchMidnights, and AdmitDay columns on the Stays sheet as you go. B2, B4, and B5 also use your LOSDays column from task 7.</t>
@@ -40811,7 +40808,7 @@
         </is>
       </c>
       <c r="D6" cm="1" s="39">
-        <f t="array" ref="D6">IF(COUNT('Stays'!$K$2:$K$370)=0,"",COUNTIF('Stays'!$K$2:$K$370,"&gt;=2"))</f>
+        <f t="array" ref="D6">IF(COUNT(Stays!$K$2:$K$370)=0,"",COUNTIF(Stays!$K$2:$K$370,"&gt;=2"))</f>
         <v/>
       </c>
       <c r="E6" s="22">
@@ -40858,7 +40855,7 @@
         </is>
       </c>
       <c r="D8" cm="1" s="39">
-        <f t="array" ref="D8">IF(COUNT('Stays'!$L$2:$L$370)=0,"",COUNTIF('Stays'!$L$2:$L$370,"&gt;=2"))</f>
+        <f t="array" ref="D8">IF(COUNT(Stays!$L$2:$L$370)=0,"",COUNTIF(Stays!$L$2:$L$370,"&gt;=2"))</f>
         <v/>
       </c>
       <c r="E8" s="22">

--- a/02-formulas-functions/03-date-time-functions/2.3-date-time-functions.xlsx
+++ b/02-formulas-functions/03-date-time-functions/2.3-date-time-functions.xlsx
@@ -824,7 +824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:C35"/>
+  <dimension ref="B2:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -849,7 +849,7 @@
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Beginner → Intermediate  ·  about 55 minutes  ·  Bluestone Health System (fictional)</t>
+          <t>Beginner → Intermediate  ·  about 115 minutes  ·  Bluestone Health System (fictional)</t>
         </is>
       </c>
     </row>
@@ -1068,94 +1068,118 @@
     <row r="28" ht="18" customHeight="1">
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Stays</t>
+          <t>Practice</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Data: 369 rows, in the Excel Table 'tblStays'</t>
+          <t>13 practice tasks, each with a Check cell.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Claims</t>
+          <t>Stays</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>Data: 369 rows, in the Excel Table 'tblClaims'</t>
+          <t>Data: 369 rows, in the Excel Table 'tblStays'</t>
         </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>Claims</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Data: 226 rows, in the Excel Table 'tblED'</t>
+          <t>Data: 369 rows, in the Excel Table 'tblClaims'</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>Shifts</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Data: 185 rows, in the Excel Table 'tblShifts'</t>
+          <t>Data: 226 rows, in the Excel Table 'tblED'</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Holidays</t>
+          <t>Shifts</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Data: 18 rows, in the Excel Table 'tblHolidays'</t>
+          <t>Data: 185 rows, in the Excel Table 'tblShifts'</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="8" t="inlineStr">
         <is>
+          <t>Holidays</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Data: 18 rows, in the Excel Table 'tblHolidays'</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="B34" s="8" t="inlineStr">
+        <is>
           <t>Settings</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>Data: 1 row</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="78" customHeight="1">
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>About the data</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>All 369 inpatient stays admitted at Ashby Falls Community Hospital in 2025 (with each patient's date of birth and, for ED admissions, the ED arrival time), the insurance claim for each stay, and the hospital's 226 emergency department visits in Q4 2025. The workbook also has one pay week (December 14–20, 2025) of worked shifts on Medical-Surgical 4 West at Bluestone Memorial Hospital and the business office's 2025–2026 holiday calendar.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="B35" s="8" t="inlineStr">
         <is>
+          <t>Bonus</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>The bonus challenge (5 parts).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="78" customHeight="1">
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>About the data</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>All 369 inpatient stays admitted at Ashby Falls Community Hospital in 2025 (with each patient's date of birth and, for ED admissions, the ED arrival time), the insurance claim for each stay, and the hospital's 226 emergency department visits in Q4 2025. The workbook also has one pay week (December 14–20, 2025) of worked shifts on Medical-Surgical 4 West at Bluestone Memorial Hospital and the business office's 2025–2026 holiday calendar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="B37" s="8" t="inlineStr">
+        <is>
           <t>Disclaimer</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>All people, places, and numbers are synthetic and fictional. Not clinical guidance.</t>
         </is>

--- a/02-formulas-functions/03-date-time-functions/2.3-date-time-functions.xlsx
+++ b/02-formulas-functions/03-date-time-functions/2.3-date-time-functions.xlsx
@@ -929,7 +929,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
+    <row r="14" ht="48" customHeight="1">
       <c r="B14" s="8" t="inlineStr">
         <is>
           <t>2. Practice</t>
@@ -937,7 +937,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Go to the 'Practice' sheet. Type a formula or value into each yellow cell.</t>
+          <t>Go to the 'Practice' sheet. Type a formula or value into each yellow cell. For tasks 3, 7, 9, 12, and 13, fill the yellow column on the Stays, Claims, ED, or Shifts sheet instead, and the task's gray cell on Practice reads it.</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="F8" s="19" t="inlineStr">
         <is>
-          <t>Fill AdmitDay with =TEXT(G2,"dddd"), which returns full weekday names. AVERAGEIF averages the LOSDays values on rows where AdmitDay is "Friday", and × 24 converts days to hours. The array formula from Lesson 2.1, =ROUND(AVERAGE(IF(Stays!M2:M370="Friday",Stays!J2:J370))*24,1), also works. Microsoft 365 and Excel 2021 calculate it automatically, and Excel 2019 and earlier need Ctrl + Shift + Enter (Mac: ⌘ + Shift + Return). TEXT returns weekday names in your Office language, so a German Excel shows "Freitag".</t>
+          <t>Fill AdmitDay with =TEXT(G2,"dddd"), which returns full weekday names. AVERAGEIF averages the LOSDays values on rows where AdmitDay is "Friday", and × 24 converts days to hours. The array formula from Lesson 2.1, =ROUND(AVERAGE(IF(Stays!M2:M370="Friday",Stays!J2:J370))*24,1), also works. Microsoft 365 and Excel 2021 or later calculate it automatically, and Excel 2019 and earlier need Ctrl + Shift + Enter (Mac: ⌘ + Shift + Return). TEXT returns weekday names in your Office language, so a German Excel shows "Freitag".</t>
         </is>
       </c>
     </row>
